--- a/docs/function.xlsx
+++ b/docs/function.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="MUSTSHOULD要件一覧_2" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'MUSTSHOULD要件一覧_2'!$A$1:$A$38</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'MUSTSHOULD要件一覧_2'!$A$1:$A$44</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="59">
   <si>
     <t>画面</t>
   </si>
@@ -45,6 +45,12 @@
     <t>↑タップ遷移　アニメーション_1</t>
   </si>
   <si>
+    <t>同期</t>
+  </si>
+  <si>
+    <t>いずれか1台の有効タッチで全4面同期遷移</t>
+  </si>
+  <si>
     <t>アニメーション_1</t>
   </si>
   <si>
@@ -57,7 +63,13 @@
     <t>自動遷移　探索画面</t>
   </si>
   <si>
+    <t>4面同期再生</t>
+  </si>
+  <si>
     <t>探索画面</t>
+  </si>
+  <si>
+    <t>探索開始後は各モニター独立操作</t>
   </si>
   <si>
     <t>40〜70枚の画像をランダム配置（サイズ不均一・グレースケール）</t>
@@ -105,7 +117,7 @@
     <t>TRUNKロゴ（画像）</t>
   </si>
   <si>
-    <t>画像拡大画面</t>
+    <t>画像拡大モーダル</t>
   </si>
   <si>
     <t>フルスクリーン画像表示</t>
@@ -117,7 +129,7 @@
     <t>↑ ×タップ遷移　探索画面</t>
   </si>
   <si>
-    <t>カテゴリ画面</t>
+    <t>カテゴリドロワー</t>
   </si>
   <si>
     <t>カテゴリ一覧表示 （テキスト）</t>
@@ -144,10 +156,19 @@
     <t>上下スワイプでスクロール</t>
   </si>
   <si>
+    <t>スクロールで詳細セクション切替</t>
+  </si>
+  <si>
     <t>×で閉じる→カテゴリ画面へ</t>
   </si>
   <si>
     <t>↑xタップ遷移　カテゴリ画面</t>
+  </si>
+  <si>
+    <t>状態管理</t>
+  </si>
+  <si>
+    <t>同一画面内スクロール（scrollSection）で管理</t>
   </si>
   <si>
     <t>共通UI</t>
@@ -157,6 +178,9 @@
   </si>
   <si>
     <t>システム</t>
+  </si>
+  <si>
+    <t>無操作時のTOP復帰/スリープ復帰仕様は検討中</t>
   </si>
   <si>
     <t>画像・動画コンテンツ表示</t>
@@ -185,7 +209,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -198,6 +222,12 @@
         <bgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE599"/>
+        <bgColor rgb="FFFFE599"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border/>
@@ -205,12 +235,18 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -571,14 +607,14 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -606,13 +642,13 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -640,10 +676,10 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>15</v>
@@ -673,13 +709,13 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="1"/>
@@ -707,14 +743,14 @@
       <c r="Z8" s="1"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>17</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -742,13 +778,13 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -776,13 +812,13 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -810,13 +846,13 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -844,13 +880,13 @@
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -878,13 +914,13 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -912,10 +948,10 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>24</v>
@@ -946,10 +982,10 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>25</v>
@@ -980,10 +1016,10 @@
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>26</v>
@@ -1014,13 +1050,13 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -1048,13 +1084,13 @@
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -1082,13 +1118,13 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -1116,10 +1152,10 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>31</v>
@@ -1150,13 +1186,13 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -1184,13 +1220,13 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -1217,14 +1253,14 @@
       <c r="Z23" s="1"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="1" t="s">
-        <v>30</v>
+      <c r="A24" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -1251,14 +1287,14 @@
       <c r="Z24" s="1"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -1285,7 +1321,7 @@
       <c r="Z25" s="1"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -1319,11 +1355,11 @@
       <c r="Z26" s="1"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>37</v>
@@ -1353,14 +1389,14 @@
       <c r="Z27" s="1"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="1" t="s">
-        <v>34</v>
+      <c r="A28" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -1387,11 +1423,11 @@
       <c r="Z28" s="1"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="1" t="s">
-        <v>39</v>
+      <c r="A29" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>40</v>
@@ -1421,11 +1457,11 @@
       <c r="Z29" s="1"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="1" t="s">
-        <v>39</v>
+      <c r="A30" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>41</v>
@@ -1455,14 +1491,14 @@
       <c r="Z30" s="1"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="1" t="s">
-        <v>39</v>
+      <c r="A31" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -1490,13 +1526,13 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -1524,13 +1560,13 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -1558,13 +1594,13 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -1591,13 +1627,13 @@
       <c r="Z34" s="1"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="A35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D35" s="1"/>
@@ -1625,14 +1661,14 @@
       <c r="Z35" s="1"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -1660,13 +1696,13 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -1694,13 +1730,13 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -1727,9 +1763,15 @@
       <c r="Z38" s="1"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
+      <c r="A39" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -1755,9 +1797,15 @@
       <c r="Z39" s="1"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
+      <c r="A40" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
@@ -1783,9 +1831,15 @@
       <c r="Z40" s="1"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
+      <c r="A41" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
@@ -1811,9 +1865,15 @@
       <c r="Z41" s="1"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
+      <c r="A42" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
@@ -1839,9 +1899,15 @@
       <c r="Z42" s="1"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
+      <c r="A43" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
@@ -1867,9 +1933,15 @@
       <c r="Z43" s="1"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
+      <c r="A44" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -7326,12 +7398,174 @@
       <c r="Y238" s="1"/>
       <c r="Z238" s="1"/>
     </row>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1">
+      <c r="A239" s="1"/>
+      <c r="B239" s="1"/>
+      <c r="C239" s="1"/>
+      <c r="D239" s="1"/>
+      <c r="E239" s="1"/>
+      <c r="F239" s="1"/>
+      <c r="G239" s="1"/>
+      <c r="H239" s="1"/>
+      <c r="I239" s="1"/>
+      <c r="J239" s="1"/>
+      <c r="K239" s="1"/>
+      <c r="L239" s="1"/>
+      <c r="M239" s="1"/>
+      <c r="N239" s="1"/>
+      <c r="O239" s="1"/>
+      <c r="P239" s="1"/>
+      <c r="Q239" s="1"/>
+      <c r="R239" s="1"/>
+      <c r="S239" s="1"/>
+      <c r="T239" s="1"/>
+      <c r="U239" s="1"/>
+      <c r="V239" s="1"/>
+      <c r="W239" s="1"/>
+      <c r="X239" s="1"/>
+      <c r="Y239" s="1"/>
+      <c r="Z239" s="1"/>
+    </row>
+    <row r="240" ht="15.75" customHeight="1">
+      <c r="A240" s="1"/>
+      <c r="B240" s="1"/>
+      <c r="C240" s="1"/>
+      <c r="D240" s="1"/>
+      <c r="E240" s="1"/>
+      <c r="F240" s="1"/>
+      <c r="G240" s="1"/>
+      <c r="H240" s="1"/>
+      <c r="I240" s="1"/>
+      <c r="J240" s="1"/>
+      <c r="K240" s="1"/>
+      <c r="L240" s="1"/>
+      <c r="M240" s="1"/>
+      <c r="N240" s="1"/>
+      <c r="O240" s="1"/>
+      <c r="P240" s="1"/>
+      <c r="Q240" s="1"/>
+      <c r="R240" s="1"/>
+      <c r="S240" s="1"/>
+      <c r="T240" s="1"/>
+      <c r="U240" s="1"/>
+      <c r="V240" s="1"/>
+      <c r="W240" s="1"/>
+      <c r="X240" s="1"/>
+      <c r="Y240" s="1"/>
+      <c r="Z240" s="1"/>
+    </row>
+    <row r="241" ht="15.75" customHeight="1">
+      <c r="A241" s="1"/>
+      <c r="B241" s="1"/>
+      <c r="C241" s="1"/>
+      <c r="D241" s="1"/>
+      <c r="E241" s="1"/>
+      <c r="F241" s="1"/>
+      <c r="G241" s="1"/>
+      <c r="H241" s="1"/>
+      <c r="I241" s="1"/>
+      <c r="J241" s="1"/>
+      <c r="K241" s="1"/>
+      <c r="L241" s="1"/>
+      <c r="M241" s="1"/>
+      <c r="N241" s="1"/>
+      <c r="O241" s="1"/>
+      <c r="P241" s="1"/>
+      <c r="Q241" s="1"/>
+      <c r="R241" s="1"/>
+      <c r="S241" s="1"/>
+      <c r="T241" s="1"/>
+      <c r="U241" s="1"/>
+      <c r="V241" s="1"/>
+      <c r="W241" s="1"/>
+      <c r="X241" s="1"/>
+      <c r="Y241" s="1"/>
+      <c r="Z241" s="1"/>
+    </row>
+    <row r="242" ht="15.75" customHeight="1">
+      <c r="A242" s="1"/>
+      <c r="B242" s="1"/>
+      <c r="C242" s="1"/>
+      <c r="D242" s="1"/>
+      <c r="E242" s="1"/>
+      <c r="F242" s="1"/>
+      <c r="G242" s="1"/>
+      <c r="H242" s="1"/>
+      <c r="I242" s="1"/>
+      <c r="J242" s="1"/>
+      <c r="K242" s="1"/>
+      <c r="L242" s="1"/>
+      <c r="M242" s="1"/>
+      <c r="N242" s="1"/>
+      <c r="O242" s="1"/>
+      <c r="P242" s="1"/>
+      <c r="Q242" s="1"/>
+      <c r="R242" s="1"/>
+      <c r="S242" s="1"/>
+      <c r="T242" s="1"/>
+      <c r="U242" s="1"/>
+      <c r="V242" s="1"/>
+      <c r="W242" s="1"/>
+      <c r="X242" s="1"/>
+      <c r="Y242" s="1"/>
+      <c r="Z242" s="1"/>
+    </row>
+    <row r="243" ht="15.75" customHeight="1">
+      <c r="A243" s="1"/>
+      <c r="B243" s="1"/>
+      <c r="C243" s="1"/>
+      <c r="D243" s="1"/>
+      <c r="E243" s="1"/>
+      <c r="F243" s="1"/>
+      <c r="G243" s="1"/>
+      <c r="H243" s="1"/>
+      <c r="I243" s="1"/>
+      <c r="J243" s="1"/>
+      <c r="K243" s="1"/>
+      <c r="L243" s="1"/>
+      <c r="M243" s="1"/>
+      <c r="N243" s="1"/>
+      <c r="O243" s="1"/>
+      <c r="P243" s="1"/>
+      <c r="Q243" s="1"/>
+      <c r="R243" s="1"/>
+      <c r="S243" s="1"/>
+      <c r="T243" s="1"/>
+      <c r="U243" s="1"/>
+      <c r="V243" s="1"/>
+      <c r="W243" s="1"/>
+      <c r="X243" s="1"/>
+      <c r="Y243" s="1"/>
+      <c r="Z243" s="1"/>
+    </row>
+    <row r="244" ht="15.75" customHeight="1">
+      <c r="A244" s="1"/>
+      <c r="B244" s="1"/>
+      <c r="C244" s="1"/>
+      <c r="D244" s="1"/>
+      <c r="E244" s="1"/>
+      <c r="F244" s="1"/>
+      <c r="G244" s="1"/>
+      <c r="H244" s="1"/>
+      <c r="I244" s="1"/>
+      <c r="J244" s="1"/>
+      <c r="K244" s="1"/>
+      <c r="L244" s="1"/>
+      <c r="M244" s="1"/>
+      <c r="N244" s="1"/>
+      <c r="O244" s="1"/>
+      <c r="P244" s="1"/>
+      <c r="Q244" s="1"/>
+      <c r="R244" s="1"/>
+      <c r="S244" s="1"/>
+      <c r="T244" s="1"/>
+      <c r="U244" s="1"/>
+      <c r="V244" s="1"/>
+      <c r="W244" s="1"/>
+      <c r="X244" s="1"/>
+      <c r="Y244" s="1"/>
+      <c r="Z244" s="1"/>
+    </row>
     <row r="245" ht="15.75" customHeight="1"/>
     <row r="246" ht="15.75" customHeight="1"/>
     <row r="247" ht="15.75" customHeight="1"/>
@@ -8086,14 +8320,20 @@
     <row r="996" ht="15.75" customHeight="1"/>
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$1:$A$38"/>
+  <autoFilter ref="$A$1:$A$44"/>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A2:A38">
-      <formula1>"探索画面,カテゴリ画面,詳細画面,画像拡大画面,共通UI,システム,パフォーマンス,スリープ画面,祝祭演出,アニメーション_1,アニメーション_2,詳細画面_2"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A2:A44">
+      <formula1>"探索画面,カテゴリドロワー,詳細画面,画像拡大モーダル,共通UI,システム,パフォーマンス,スリープ画面,祝祭演出,アニメーション_1,アニメーション_2,詳細画面_2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B38">
-      <formula1>"ナビゲーション,演出,機能,操作,表示,要件"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B44">
+      <formula1>"ナビゲーション,演出,機能,操作,表示,要件,状態管理,同期"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions/>
